--- a/backend/storage/imports/Master_SBM/12. SATUAN BIAYA PENGGANTIAN INVENTARIS LAMA DAN ATAU PEMBELIAN INVENTARIS UNTUK PEGAWAI BARU.xlsx
+++ b/backend/storage/imports/Master_SBM/12. SATUAN BIAYA PENGGANTIAN INVENTARIS LAMA DAN ATAU PEMBELIAN INVENTARIS UNTUK PEGAWAI BARU.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="X:\dokumen perkuliahan\kebutuhan magang\Projek magang\DITUGASKAN\SBM\imports\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="X:\dokumen perkuliahan\kebutuhan magang\Projek magang\DITUGASKAN\SBM\baru 1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5205A8C0-8175-4B1D-8680-4C5CB925E080}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C9539090-2DA4-4F61-A74A-5777DFC2A520}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{707DCBBE-017A-4FD2-BCC7-1FA97DC339AC}"/>
   </bookViews>
